--- a/docs/detail-design/16_LichLam.xlsx
+++ b/docs/detail-design/16_LichLam.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="207">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · LỊCH LÀM</t>
   </si>
@@ -137,6 +137,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Form ca / ca mẫu: ô thiếu viền đỏ + hộp lỗi "Vui lòng nhập đủ các ô bắt buộc" khi lưu.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Lịch làm tuần này (Quản lý)</t>
   </si>
   <si>
@@ -635,7 +641,7 @@
     <t>404 "Không tìm thấy ca mẫu"</t>
   </si>
   <si>
-    <t>Lỗi hiện trong form đang mở (ca / ca mẫu) hoặc hộp đỏ phía trên bảng. Không ghi nhật ký thao tác (cấu hình), vẫn có created/updated by.</t>
+    <t>Lỗi hiện trong form đang mở (ca / ca mẫu) hoặc hộp đỏ phía trên bảng. Bấm Lưu khi thiếu ô bắt buộc (giờ bắt đầu / kết thúc, tên ca): ô viền đỏ + "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", không gửi. Không ghi nhật ký thao tác (cấu hình), vẫn có created/updated by.</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1272,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1997,8 +2003,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -2038,6 +2086,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -2057,7 +2109,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2093,7 +2145,7 @@
     </row>
     <row r="54" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -2129,7 +2181,7 @@
     </row>
     <row r="114" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B114" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -2165,7 +2217,7 @@
     </row>
     <row r="143" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
@@ -2225,7 +2277,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2261,10 +2313,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2275,22 +2327,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2298,12 +2350,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2316,33 +2368,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2350,12 +2402,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2368,33 +2420,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2402,12 +2454,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2420,33 +2472,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2454,12 +2506,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2472,33 +2524,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2506,12 +2558,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2524,33 +2576,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2558,12 +2610,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2576,33 +2628,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2610,12 +2662,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2628,33 +2680,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2662,12 +2714,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2680,33 +2732,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2714,12 +2766,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2732,33 +2784,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2766,12 +2818,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2784,33 +2836,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2818,12 +2870,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2836,33 +2888,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2870,12 +2922,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2888,33 +2940,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2922,12 +2974,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2940,33 +2992,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2974,12 +3026,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2992,33 +3044,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -3026,12 +3078,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -3044,33 +3096,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -3078,12 +3130,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -3096,33 +3148,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -3130,12 +3182,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -3145,7 +3197,7 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -3181,10 +3233,10 @@
     </row>
     <row r="21" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3195,22 +3247,22 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -3218,12 +3270,12 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
       <c r="AB21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
@@ -3236,33 +3288,33 @@
         <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -3270,12 +3322,12 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -3288,33 +3340,33 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3322,12 +3374,12 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -3340,33 +3392,33 @@
         <v>19</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -3374,12 +3426,12 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -3392,33 +3444,33 @@
         <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3426,12 +3478,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3444,33 +3496,33 @@
         <v>21</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -3478,12 +3530,12 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -3496,33 +3548,33 @@
         <v>22</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -3530,12 +3582,12 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3545,7 +3597,7 @@
     </row>
     <row r="29" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -3581,10 +3633,10 @@
     </row>
     <row r="30" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -3595,22 +3647,22 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3618,12 +3670,12 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
       <c r="AB30" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
@@ -3636,33 +3688,33 @@
         <v>23</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
@@ -3670,12 +3722,12 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
       <c r="AB31" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3688,33 +3740,33 @@
         <v>24</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R32" s="3"/>
       <c r="S32" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
@@ -3722,12 +3774,12 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
       <c r="AB32" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3740,33 +3792,33 @@
         <v>25</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -3774,12 +3826,12 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3792,33 +3844,33 @@
         <v>26</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -3826,12 +3878,12 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3844,33 +3896,33 @@
         <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
@@ -3878,12 +3930,12 @@
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3893,7 +3945,7 @@
     </row>
     <row r="37" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3929,10 +3981,10 @@
     </row>
     <row r="38" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -3943,22 +3995,22 @@
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R38" s="5"/>
       <c r="S38" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -3966,12 +4018,12 @@
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
       <c r="AB38" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC38" s="5"/>
       <c r="AD38" s="5"/>
@@ -3984,33 +4036,33 @@
         <v>28</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P39" s="3"/>
       <c r="Q39" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R39" s="3"/>
       <c r="S39" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
@@ -4018,12 +4070,12 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -4312,7 +4364,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4348,7 +4400,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -4384,10 +4436,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -4422,10 +4474,10 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -4460,10 +4512,10 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -4498,7 +4550,7 @@
     </row>
     <row r="7" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4534,10 +4586,10 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -4572,10 +4624,10 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -4610,10 +4662,10 @@
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -4648,10 +4700,10 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -4686,10 +4738,10 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -4724,10 +4776,10 @@
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -4762,7 +4814,7 @@
     </row>
     <row r="15" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -4798,10 +4850,10 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -4836,10 +4888,10 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -4874,10 +4926,10 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -4912,10 +4964,10 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -4950,10 +5002,10 @@
     </row>
     <row r="20" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -4988,7 +5040,7 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -5024,7 +5076,7 @@
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -5032,7 +5084,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -5043,7 +5095,7 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -5064,7 +5116,7 @@
     </row>
     <row r="24" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5072,7 +5124,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -5083,7 +5135,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -5104,7 +5156,7 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5112,7 +5164,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -5123,7 +5175,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -5144,7 +5196,7 @@
     </row>
     <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5152,7 +5204,7 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -5163,7 +5215,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -5184,7 +5236,7 @@
     </row>
     <row r="27" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5192,7 +5244,7 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -5203,7 +5255,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
@@ -5224,7 +5276,7 @@
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5232,7 +5284,7 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -5243,7 +5295,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -5262,9 +5314,9 @@
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="29" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
